--- a/reports/pdf_change_20260716.xlsx
+++ b/reports/pdf_change_20260716.xlsx
@@ -541,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K37"/>
+  <dimension ref="A1:K41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -567,14 +567,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>캡처 4/7  ·  대기: TIME, TIME, TIGER</t>
+          <t>캡처 6/7  ·  대기: TIGER</t>
         </is>
       </c>
     </row>
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,585억   ·   현금 61억(1.3%)      당일 2026-07-16  vs  전영업일 2026-07-15      매수 12종목  /  매도 11종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,921억   ·   현금 61억(1.3%)      당일 2026-07-16  vs  전영업일 2026-07-15      매수 12종목  /  매도 11종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -670,7 +670,7 @@
         <v>211</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>9154024000</v>
+        <v>9135456000</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         <v>-34</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-452238760</v>
+        <v>-451321440</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>106</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>1639856040</v>
+        <v>1636529760</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>-24</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-992704800</v>
+        <v>-990691200</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
         <v>59</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>1111705140</v>
+        <v>1109450160</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>-16</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-416486400</v>
+        <v>-415641600</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>51</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>509900040</v>
+        <v>508865760</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         <v>-16</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-484323200</v>
+        <v>-483340800</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
         <v>37</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>481562400</v>
+        <v>480585600</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>-15</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-420036000</v>
+        <v>-419184000</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>33</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>2599786200</v>
+        <v>2594512800</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>-14</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-934530800</v>
+        <v>-932635200</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>23</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>717758700</v>
+        <v>716302800</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>-10</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>-2110040000</v>
+        <v>-2105760000</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>18</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>974365200</v>
+        <v>972388800</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
@@ -992,23 +992,23 @@
       </c>
       <c r="G13" s="14" t="inlineStr">
         <is>
-          <t>에스앤에스텍</t>
+          <t>에이치브이엠</t>
         </is>
       </c>
       <c r="H13" s="15" t="n">
         <v>-10</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-471308000</v>
+        <v>-427056000</v>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
-          <t>0.45%→0.34%</t>
+          <t>0.32%→0.21%</t>
         </is>
       </c>
       <c r="K13" s="13" t="inlineStr">
         <is>
-          <t>45→35</t>
+          <t>34→24</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
         <v>17</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>947053000</v>
+        <v>945132000</v>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
@@ -1036,23 +1036,23 @@
       </c>
       <c r="G14" s="14" t="inlineStr">
         <is>
-          <t>에이치브이엠</t>
+          <t>에스앤에스텍</t>
         </is>
       </c>
       <c r="H14" s="15" t="n">
         <v>-10</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-427924000</v>
+        <v>-470352000</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
-          <t>0.32%→0.21%</t>
+          <t>0.45%→0.34%</t>
         </is>
       </c>
       <c r="K14" s="13" t="inlineStr">
         <is>
-          <t>34→24</t>
+          <t>45→35</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
         <v>16</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>2464211200</v>
+        <v>2459212800</v>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>-7</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-984915400</v>
+        <v>-982917600</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>11</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>458243500</v>
+        <v>457314000</v>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>-6</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-229245000</v>
+        <v>-228780000</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
         <v>3</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>494281800</v>
+        <v>493279200</v>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
@@ -1175,7 +1175,7 @@
     <row r="19" ht="19" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 4,024억   ·   현금 11억(0.3%)      당일 2026-07-16  vs  전영업일 2026-07-15      매수 0종목  /  매도 0종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 4,238억   ·   현금 11억(0.3%)      당일 2026-07-16  vs  전영업일 2026-07-15      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B19" s="4" t="n"/>
@@ -1197,329 +1197,439 @@
       </c>
     </row>
     <row r="22" ht="19" customHeight="1">
-      <c r="A22" s="19" t="inlineStr">
-        <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B22" s="20" t="n"/>
-      <c r="C22" s="20" t="n"/>
-      <c r="D22" s="20" t="n"/>
-      <c r="E22" s="20" t="n"/>
-      <c r="F22" s="20" t="n"/>
-      <c r="G22" s="20" t="n"/>
-      <c r="H22" s="20" t="n"/>
-      <c r="I22" s="20" t="n"/>
-      <c r="J22" s="20" t="n"/>
-      <c r="K22" s="20" t="n"/>
-    </row>
-    <row r="24" ht="19" customHeight="1">
-      <c r="A24" s="19" t="inlineStr">
-        <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B24" s="20" t="n"/>
-      <c r="C24" s="20" t="n"/>
-      <c r="D24" s="20" t="n"/>
-      <c r="E24" s="20" t="n"/>
-      <c r="F24" s="20" t="n"/>
-      <c r="G24" s="20" t="n"/>
-      <c r="H24" s="20" t="n"/>
-      <c r="I24" s="20" t="n"/>
-      <c r="J24" s="20" t="n"/>
-      <c r="K24" s="20" t="n"/>
-    </row>
-    <row r="26" ht="19" customHeight="1">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 341억   ·   현금 2억(100.0%)      당일 2026-07-16  vs  전영업일 2026-07-15      매수 2종목  /  매도 4종목</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="n"/>
-      <c r="C26" s="4" t="n"/>
-      <c r="D26" s="4" t="n"/>
-      <c r="E26" s="4" t="n"/>
-      <c r="F26" s="4" t="n"/>
-      <c r="G26" s="4" t="n"/>
-      <c r="H26" s="4" t="n"/>
-      <c r="I26" s="4" t="n"/>
-      <c r="J26" s="4" t="n"/>
-      <c r="K26" s="4" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,884억   ·   현금 28억(1.0%)      당일 2026-07-16  vs  전영업일 2026-07-15      매수 1종목  /  매도 0종목</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="n"/>
+      <c r="C22" s="4" t="n"/>
+      <c r="D22" s="4" t="n"/>
+      <c r="E22" s="4" t="n"/>
+      <c r="F22" s="4" t="n"/>
+      <c r="G22" s="4" t="n"/>
+      <c r="H22" s="4" t="n"/>
+      <c r="I22" s="4" t="n"/>
+      <c r="J22" s="4" t="n"/>
+      <c r="K22" s="4" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>🔴 매수 (확대·신규편입)</t>
         </is>
       </c>
-      <c r="B27" s="6" t="n"/>
-      <c r="C27" s="6" t="n"/>
-      <c r="D27" s="6" t="n"/>
-      <c r="E27" s="6" t="n"/>
-      <c r="G27" s="7" t="inlineStr">
+      <c r="B23" s="6" t="n"/>
+      <c r="C23" s="6" t="n"/>
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="6" t="n"/>
+      <c r="G23" s="7" t="inlineStr">
         <is>
           <t>🔵 매도 (축소·편출)</t>
         </is>
       </c>
-      <c r="H27" s="8" t="n"/>
-      <c r="I27" s="8" t="n"/>
-      <c r="J27" s="8" t="n"/>
-      <c r="K27" s="8" t="n"/>
+      <c r="H23" s="8" t="n"/>
+      <c r="I23" s="8" t="n"/>
+      <c r="J23" s="8" t="n"/>
+      <c r="K23" s="8" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E24" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G24" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H24" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I24" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J24" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K24" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>티엘비</t>
+        </is>
+      </c>
+      <c r="B25" s="11" t="n">
+        <v>122</v>
+      </c>
+      <c r="C25" s="11" t="n">
+        <v>3660976000</v>
+      </c>
+      <c r="D25" s="12" t="inlineStr">
+        <is>
+          <t>2.26%→2.58%</t>
+        </is>
+      </c>
+      <c r="E25" s="13" t="inlineStr">
+        <is>
+          <t>120→242</t>
+        </is>
+      </c>
+      <c r="G25" s="17" t="n"/>
+      <c r="H25" s="17" t="n"/>
+      <c r="I25" s="17" t="n"/>
+      <c r="J25" s="17" t="n"/>
+      <c r="K25" s="17" t="n"/>
+    </row>
+    <row r="27" ht="19" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,500억   ·   현금 27억(1.1%)      당일 2026-07-16  vs  전영업일 2026-07-15      매수 0종목  /  매도 0종목</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="n"/>
+      <c r="C27" s="4" t="n"/>
+      <c r="D27" s="4" t="n"/>
+      <c r="E27" s="4" t="n"/>
+      <c r="F27" s="4" t="n"/>
+      <c r="G27" s="4" t="n"/>
+      <c r="H27" s="4" t="n"/>
+      <c r="I27" s="4" t="n"/>
+      <c r="J27" s="4" t="n"/>
+      <c r="K27" s="4" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="9" t="inlineStr">
+      <c r="A28" s="18" t="inlineStr">
+        <is>
+          <t>변화 없음 (구성종목 동일)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="19" customHeight="1">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 359억   ·   현금 2억(100.0%)      당일 2026-07-16  vs  전영업일 2026-07-15      매수 2종목  /  매도 4종목</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="n"/>
+      <c r="C30" s="4" t="n"/>
+      <c r="D30" s="4" t="n"/>
+      <c r="E30" s="4" t="n"/>
+      <c r="F30" s="4" t="n"/>
+      <c r="G30" s="4" t="n"/>
+      <c r="H30" s="4" t="n"/>
+      <c r="I30" s="4" t="n"/>
+      <c r="J30" s="4" t="n"/>
+      <c r="K30" s="4" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+      <c r="E31" s="6" t="n"/>
+      <c r="G31" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H31" s="8" t="n"/>
+      <c r="I31" s="8" t="n"/>
+      <c r="J31" s="8" t="n"/>
+      <c r="K31" s="8" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="B28" s="9" t="inlineStr">
+      <c r="B32" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="C28" s="9" t="inlineStr">
+      <c r="C32" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="D28" s="9" t="inlineStr">
+      <c r="D32" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="E28" s="9" t="inlineStr">
+      <c r="E32" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
       </c>
-      <c r="G28" s="9" t="inlineStr">
+      <c r="G32" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="H28" s="9" t="inlineStr">
+      <c r="H32" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="I28" s="9" t="inlineStr">
+      <c r="I32" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="J28" s="9" t="inlineStr">
+      <c r="J32" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="K28" s="9" t="inlineStr">
+      <c r="K32" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="10" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="10" t="inlineStr">
         <is>
           <t>더블유씨피</t>
         </is>
       </c>
-      <c r="B29" s="11" t="n">
+      <c r="B33" s="11" t="n">
         <v>110</v>
       </c>
-      <c r="C29" s="11" t="n">
-        <v>76389500</v>
-      </c>
-      <c r="D29" s="12" t="inlineStr">
-        <is>
-          <t>6.62%→6.84%</t>
-        </is>
-      </c>
-      <c r="E29" s="13" t="inlineStr">
+      <c r="C33" s="11" t="n">
+        <v>78633500</v>
+      </c>
+      <c r="D33" s="12" t="inlineStr">
+        <is>
+          <t>6.46%→6.68%</t>
+        </is>
+      </c>
+      <c r="E33" s="13" t="inlineStr">
         <is>
           <t>3,229→3,339</t>
         </is>
       </c>
-      <c r="G29" s="14" t="inlineStr">
+      <c r="G33" s="14" t="inlineStr">
         <is>
           <t>원익IPS</t>
         </is>
       </c>
-      <c r="H29" s="15" t="n">
+      <c r="H33" s="15" t="n">
         <v>-8</v>
       </c>
-      <c r="I29" s="15" t="n">
-        <v>-86428000</v>
-      </c>
-      <c r="J29" s="16" t="inlineStr">
-        <is>
-          <t>2.97%→2.71%</t>
-        </is>
-      </c>
-      <c r="K29" s="13" t="inlineStr">
+      <c r="I33" s="15" t="n">
+        <v>-97036000</v>
+      </c>
+      <c r="J33" s="16" t="inlineStr">
+        <is>
+          <t>3.16%→2.89%</t>
+        </is>
+      </c>
+      <c r="K33" s="13" t="inlineStr">
         <is>
           <t>93→85</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="10" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="10" t="inlineStr">
         <is>
           <t>씨어스</t>
         </is>
       </c>
-      <c r="B30" s="11" t="n">
+      <c r="B34" s="11" t="n">
         <v>55</v>
       </c>
-      <c r="C30" s="11" t="n">
-        <v>147262500</v>
-      </c>
-      <c r="D30" s="12" t="inlineStr">
-        <is>
-          <t>5.67%→6.10%</t>
-        </is>
-      </c>
-      <c r="E30" s="13" t="inlineStr">
+      <c r="C34" s="11" t="n">
+        <v>151236250</v>
+      </c>
+      <c r="D34" s="12" t="inlineStr">
+        <is>
+          <t>5.52%→5.95%</t>
+        </is>
+      </c>
+      <c r="E34" s="13" t="inlineStr">
         <is>
           <t>717→772</t>
         </is>
       </c>
-      <c r="G30" s="14" t="inlineStr">
+      <c r="G34" s="14" t="inlineStr">
         <is>
           <t>피에스케이홀딩스</t>
         </is>
       </c>
-      <c r="H30" s="15" t="n">
+      <c r="H34" s="15" t="n">
         <v>-7</v>
       </c>
-      <c r="I30" s="15" t="n">
-        <v>-83895000</v>
-      </c>
-      <c r="J30" s="16" t="inlineStr">
-        <is>
-          <t>3.33%→3.08%</t>
-        </is>
-      </c>
-      <c r="K30" s="13" t="inlineStr">
+      <c r="I34" s="15" t="n">
+        <v>-92939000</v>
+      </c>
+      <c r="J34" s="16" t="inlineStr">
+        <is>
+          <t>3.49%→3.24%</t>
+        </is>
+      </c>
+      <c r="K34" s="13" t="inlineStr">
         <is>
           <t>94→87</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="17" t="n"/>
-      <c r="B31" s="17" t="n"/>
-      <c r="C31" s="17" t="n"/>
-      <c r="D31" s="17" t="n"/>
-      <c r="E31" s="17" t="n"/>
-      <c r="G31" s="14" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="17" t="n"/>
+      <c r="B35" s="17" t="n"/>
+      <c r="C35" s="17" t="n"/>
+      <c r="D35" s="17" t="n"/>
+      <c r="E35" s="17" t="n"/>
+      <c r="G35" s="14" t="inlineStr">
         <is>
           <t>브이엠</t>
         </is>
       </c>
-      <c r="H31" s="15" t="n">
+      <c r="H35" s="15" t="n">
         <v>-4</v>
       </c>
-      <c r="I31" s="15" t="n">
-        <v>-38998000</v>
-      </c>
-      <c r="J31" s="16" t="inlineStr">
-        <is>
-          <t>4.17%→4.06%</t>
-        </is>
-      </c>
-      <c r="K31" s="13" t="inlineStr">
+      <c r="I35" s="15" t="n">
+        <v>-39406000</v>
+      </c>
+      <c r="J35" s="16" t="inlineStr">
+        <is>
+          <t>4.00%→3.89%</t>
+        </is>
+      </c>
+      <c r="K35" s="13" t="inlineStr">
         <is>
           <t>145→141</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="17" t="n"/>
-      <c r="B32" s="17" t="n"/>
-      <c r="C32" s="17" t="n"/>
-      <c r="D32" s="17" t="n"/>
-      <c r="E32" s="17" t="n"/>
-      <c r="G32" s="14" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="17" t="n"/>
+      <c r="B36" s="17" t="n"/>
+      <c r="C36" s="17" t="n"/>
+      <c r="D36" s="17" t="n"/>
+      <c r="E36" s="17" t="n"/>
+      <c r="G36" s="14" t="inlineStr">
         <is>
           <t>테스</t>
         </is>
       </c>
-      <c r="H32" s="15" t="n">
+      <c r="H36" s="15" t="n">
         <v>-3</v>
       </c>
-      <c r="I32" s="15" t="n">
-        <v>-55462500</v>
-      </c>
-      <c r="J32" s="16" t="inlineStr">
-        <is>
-          <t>3.82%→3.66%</t>
-        </is>
-      </c>
-      <c r="K32" s="13" t="inlineStr">
+      <c r="I36" s="15" t="n">
+        <v>-54570000</v>
+      </c>
+      <c r="J36" s="16" t="inlineStr">
+        <is>
+          <t>3.57%→3.41%</t>
+        </is>
+      </c>
+      <c r="K36" s="13" t="inlineStr">
         <is>
           <t>70→67</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="19" customHeight="1">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 517억   ·   현금 9억(1.6%)      당일 2026-07-16  vs  전영업일 2026-07-15      매수 0종목  /  매도 0종목</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="n"/>
-      <c r="C34" s="4" t="n"/>
-      <c r="D34" s="4" t="n"/>
-      <c r="E34" s="4" t="n"/>
-      <c r="F34" s="4" t="n"/>
-      <c r="G34" s="4" t="n"/>
-      <c r="H34" s="4" t="n"/>
-      <c r="I34" s="4" t="n"/>
-      <c r="J34" s="4" t="n"/>
-      <c r="K34" s="4" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="18" t="inlineStr">
+    <row r="38" ht="19" customHeight="1">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 545억   ·   현금 9억(1.6%)      당일 2026-07-16  vs  전영업일 2026-07-15      매수 0종목  /  매도 0종목</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="n"/>
+      <c r="C38" s="4" t="n"/>
+      <c r="D38" s="4" t="n"/>
+      <c r="E38" s="4" t="n"/>
+      <c r="F38" s="4" t="n"/>
+      <c r="G38" s="4" t="n"/>
+      <c r="H38" s="4" t="n"/>
+      <c r="I38" s="4" t="n"/>
+      <c r="J38" s="4" t="n"/>
+      <c r="K38" s="4" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="18" t="inlineStr">
         <is>
           <t>변화 없음 (구성종목 동일)</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="19" customHeight="1">
-      <c r="A37" s="19" t="inlineStr">
+    <row r="41" ht="19" customHeight="1">
+      <c r="A41" s="19" t="inlineStr">
         <is>
           <t>■ TIGER 기술이전바이오액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B37" s="20" t="n"/>
-      <c r="C37" s="20" t="n"/>
-      <c r="D37" s="20" t="n"/>
-      <c r="E37" s="20" t="n"/>
-      <c r="F37" s="20" t="n"/>
-      <c r="G37" s="20" t="n"/>
-      <c r="H37" s="20" t="n"/>
-      <c r="I37" s="20" t="n"/>
-      <c r="J37" s="20" t="n"/>
-      <c r="K37" s="20" t="n"/>
+      <c r="B41" s="20" t="n"/>
+      <c r="C41" s="20" t="n"/>
+      <c r="D41" s="20" t="n"/>
+      <c r="E41" s="20" t="n"/>
+      <c r="F41" s="20" t="n"/>
+      <c r="G41" s="20" t="n"/>
+      <c r="H41" s="20" t="n"/>
+      <c r="I41" s="20" t="n"/>
+      <c r="J41" s="20" t="n"/>
+      <c r="K41" s="20" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="18">
     <mergeCell ref="A22:K22"/>
-    <mergeCell ref="A34:K34"/>
     <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A35:K35"/>
     <mergeCell ref="A3:K3"/>
     <mergeCell ref="A20:K20"/>
-    <mergeCell ref="A26:K26"/>
-    <mergeCell ref="A24:K24"/>
+    <mergeCell ref="A27:K27"/>
+    <mergeCell ref="A30:K30"/>
+    <mergeCell ref="A39:K39"/>
+    <mergeCell ref="A38:K38"/>
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A19:K19"/>
-    <mergeCell ref="G27:K27"/>
+    <mergeCell ref="A41:K41"/>
+    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="A28:K28"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="G31:K31"/>
+    <mergeCell ref="G23:K23"/>
     <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A37:K37"/>
-    <mergeCell ref="A27:E27"/>
     <mergeCell ref="G4:K4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/pdf_change_20260716.xlsx
+++ b/reports/pdf_change_20260716.xlsx
@@ -948,23 +948,23 @@
       </c>
       <c r="G12" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>에스앤에스텍</t>
         </is>
       </c>
       <c r="H12" s="15" t="n">
         <v>-10</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>-2105760000</v>
+        <v>-470352000</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
-          <t>11.65%→10.22%</t>
+          <t>0.45%→0.34%</t>
         </is>
       </c>
       <c r="K12" s="13" t="inlineStr">
         <is>
-          <t>244→234</t>
+          <t>45→35</t>
         </is>
       </c>
     </row>
@@ -992,23 +992,23 @@
       </c>
       <c r="G13" s="14" t="inlineStr">
         <is>
-          <t>에이치브이엠</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H13" s="15" t="n">
         <v>-10</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-427056000</v>
+        <v>-2105760000</v>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
-          <t>0.32%→0.21%</t>
+          <t>11.65%→10.22%</t>
         </is>
       </c>
       <c r="K13" s="13" t="inlineStr">
         <is>
-          <t>34→24</t>
+          <t>244→234</t>
         </is>
       </c>
     </row>
@@ -1036,23 +1036,23 @@
       </c>
       <c r="G14" s="14" t="inlineStr">
         <is>
-          <t>에스앤에스텍</t>
+          <t>에이치브이엠</t>
         </is>
       </c>
       <c r="H14" s="15" t="n">
         <v>-10</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-470352000</v>
+        <v>-427056000</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
-          <t>0.45%→0.34%</t>
+          <t>0.32%→0.21%</t>
         </is>
       </c>
       <c r="K14" s="13" t="inlineStr">
         <is>
-          <t>45→35</t>
+          <t>34→24</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_change_20260716.xlsx
+++ b/reports/pdf_change_20260716.xlsx
@@ -574,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,921억   ·   현금 61억(1.3%)      당일 2026-07-16  vs  전영업일 2026-07-15      매수 12종목  /  매도 11종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      당일 2026-07-16  vs  전영업일 2026-07-15      매수 12종목  /  매도 11종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -669,8 +669,10 @@
       <c r="B6" s="11" t="n">
         <v>211</v>
       </c>
-      <c r="C6" s="11" t="n">
-        <v>9135456000</v>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -690,8 +692,10 @@
       <c r="H6" s="15" t="n">
         <v>-34</v>
       </c>
-      <c r="I6" s="15" t="n">
-        <v>-451321440</v>
+      <c r="I6" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -713,8 +717,10 @@
       <c r="B7" s="11" t="n">
         <v>106</v>
       </c>
-      <c r="C7" s="11" t="n">
-        <v>1636529760</v>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -734,8 +740,10 @@
       <c r="H7" s="15" t="n">
         <v>-24</v>
       </c>
-      <c r="I7" s="15" t="n">
-        <v>-990691200</v>
+      <c r="I7" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -757,8 +765,10 @@
       <c r="B8" s="11" t="n">
         <v>59</v>
       </c>
-      <c r="C8" s="11" t="n">
-        <v>1109450160</v>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -778,8 +788,10 @@
       <c r="H8" s="15" t="n">
         <v>-16</v>
       </c>
-      <c r="I8" s="15" t="n">
-        <v>-415641600</v>
+      <c r="I8" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -801,8 +813,10 @@
       <c r="B9" s="11" t="n">
         <v>51</v>
       </c>
-      <c r="C9" s="11" t="n">
-        <v>508865760</v>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
@@ -822,8 +836,10 @@
       <c r="H9" s="15" t="n">
         <v>-16</v>
       </c>
-      <c r="I9" s="15" t="n">
-        <v>-483340800</v>
+      <c r="I9" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
@@ -845,8 +861,10 @@
       <c r="B10" s="11" t="n">
         <v>37</v>
       </c>
-      <c r="C10" s="11" t="n">
-        <v>480585600</v>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
@@ -866,8 +884,10 @@
       <c r="H10" s="15" t="n">
         <v>-15</v>
       </c>
-      <c r="I10" s="15" t="n">
-        <v>-419184000</v>
+      <c r="I10" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
@@ -889,8 +909,10 @@
       <c r="B11" s="11" t="n">
         <v>33</v>
       </c>
-      <c r="C11" s="11" t="n">
-        <v>2594512800</v>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
@@ -910,8 +932,10 @@
       <c r="H11" s="15" t="n">
         <v>-14</v>
       </c>
-      <c r="I11" s="15" t="n">
-        <v>-932635200</v>
+      <c r="I11" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
@@ -933,8 +957,10 @@
       <c r="B12" s="11" t="n">
         <v>23</v>
       </c>
-      <c r="C12" s="11" t="n">
-        <v>716302800</v>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
@@ -948,23 +974,25 @@
       </c>
       <c r="G12" s="14" t="inlineStr">
         <is>
-          <t>에스앤에스텍</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H12" s="15" t="n">
         <v>-10</v>
       </c>
-      <c r="I12" s="15" t="n">
-        <v>-470352000</v>
+      <c r="I12" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
-          <t>0.45%→0.34%</t>
+          <t>11.65%→10.22%</t>
         </is>
       </c>
       <c r="K12" s="13" t="inlineStr">
         <is>
-          <t>45→35</t>
+          <t>244→234</t>
         </is>
       </c>
     </row>
@@ -977,8 +1005,10 @@
       <c r="B13" s="11" t="n">
         <v>18</v>
       </c>
-      <c r="C13" s="11" t="n">
-        <v>972388800</v>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
@@ -992,23 +1022,25 @@
       </c>
       <c r="G13" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>에스앤에스텍</t>
         </is>
       </c>
       <c r="H13" s="15" t="n">
         <v>-10</v>
       </c>
-      <c r="I13" s="15" t="n">
-        <v>-2105760000</v>
+      <c r="I13" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
-          <t>11.65%→10.22%</t>
+          <t>0.45%→0.34%</t>
         </is>
       </c>
       <c r="K13" s="13" t="inlineStr">
         <is>
-          <t>244→234</t>
+          <t>45→35</t>
         </is>
       </c>
     </row>
@@ -1021,8 +1053,10 @@
       <c r="B14" s="11" t="n">
         <v>17</v>
       </c>
-      <c r="C14" s="11" t="n">
-        <v>945132000</v>
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
@@ -1042,8 +1076,10 @@
       <c r="H14" s="15" t="n">
         <v>-10</v>
       </c>
-      <c r="I14" s="15" t="n">
-        <v>-427056000</v>
+      <c r="I14" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
@@ -1065,8 +1101,10 @@
       <c r="B15" s="11" t="n">
         <v>16</v>
       </c>
-      <c r="C15" s="11" t="n">
-        <v>2459212800</v>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
@@ -1086,8 +1124,10 @@
       <c r="H15" s="15" t="n">
         <v>-7</v>
       </c>
-      <c r="I15" s="15" t="n">
-        <v>-982917600</v>
+      <c r="I15" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
@@ -1109,8 +1149,10 @@
       <c r="B16" s="11" t="n">
         <v>11</v>
       </c>
-      <c r="C16" s="11" t="n">
-        <v>457314000</v>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
@@ -1130,8 +1172,10 @@
       <c r="H16" s="15" t="n">
         <v>-6</v>
       </c>
-      <c r="I16" s="15" t="n">
-        <v>-228780000</v>
+      <c r="I16" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
@@ -1153,8 +1197,10 @@
       <c r="B17" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="C17" s="11" t="n">
-        <v>493279200</v>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
@@ -1175,7 +1221,7 @@
     <row r="19" ht="19" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 4,238억   ·   현금 11억(0.3%)      당일 2026-07-16  vs  전영업일 2026-07-15      매수 0종목  /  매도 0종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      당일 2026-07-16  vs  전영업일 2026-07-15      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B19" s="4" t="n"/>
@@ -1199,7 +1245,7 @@
     <row r="22" ht="19" customHeight="1">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,884억   ·   현금 28억(1.0%)      당일 2026-07-16  vs  전영업일 2026-07-15      매수 1종목  /  매도 0종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      당일 2026-07-16  vs  전영업일 2026-07-15      매수 1종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B22" s="4" t="n"/>
@@ -1294,8 +1340,10 @@
       <c r="B25" s="11" t="n">
         <v>122</v>
       </c>
-      <c r="C25" s="11" t="n">
-        <v>3660976000</v>
+      <c r="C25" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
@@ -1316,7 +1364,7 @@
     <row r="27" ht="19" customHeight="1">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,500억   ·   현금 27억(1.1%)      당일 2026-07-16  vs  전영업일 2026-07-15      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      당일 2026-07-16  vs  전영업일 2026-07-15      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B27" s="4" t="n"/>
@@ -1340,7 +1388,7 @@
     <row r="30" ht="19" customHeight="1">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 359억   ·   현금 2억(100.0%)      당일 2026-07-16  vs  전영업일 2026-07-15      매수 2종목  /  매도 4종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      당일 2026-07-16  vs  전영업일 2026-07-15      매수 2종목  /  매도 4종목</t>
         </is>
       </c>
       <c r="B30" s="4" t="n"/>
@@ -1435,12 +1483,14 @@
       <c r="B33" s="11" t="n">
         <v>110</v>
       </c>
-      <c r="C33" s="11" t="n">
-        <v>78633500</v>
+      <c r="C33" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>6.46%→6.68%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E33" s="13" t="inlineStr">
@@ -1456,12 +1506,14 @@
       <c r="H33" s="15" t="n">
         <v>-8</v>
       </c>
-      <c r="I33" s="15" t="n">
-        <v>-97036000</v>
+      <c r="I33" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J33" s="16" t="inlineStr">
         <is>
-          <t>3.16%→2.89%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K33" s="13" t="inlineStr">
@@ -1479,12 +1531,14 @@
       <c r="B34" s="11" t="n">
         <v>55</v>
       </c>
-      <c r="C34" s="11" t="n">
-        <v>151236250</v>
+      <c r="C34" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
-          <t>5.52%→5.95%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E34" s="13" t="inlineStr">
@@ -1500,12 +1554,14 @@
       <c r="H34" s="15" t="n">
         <v>-7</v>
       </c>
-      <c r="I34" s="15" t="n">
-        <v>-92939000</v>
+      <c r="I34" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J34" s="16" t="inlineStr">
         <is>
-          <t>3.49%→3.24%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K34" s="13" t="inlineStr">
@@ -1528,12 +1584,14 @@
       <c r="H35" s="15" t="n">
         <v>-4</v>
       </c>
-      <c r="I35" s="15" t="n">
-        <v>-39406000</v>
+      <c r="I35" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J35" s="16" t="inlineStr">
         <is>
-          <t>4.00%→3.89%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K35" s="13" t="inlineStr">
@@ -1556,12 +1614,14 @@
       <c r="H36" s="15" t="n">
         <v>-3</v>
       </c>
-      <c r="I36" s="15" t="n">
-        <v>-54570000</v>
+      <c r="I36" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J36" s="16" t="inlineStr">
         <is>
-          <t>3.57%→3.41%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K36" s="13" t="inlineStr">
@@ -1573,7 +1633,7 @@
     <row r="38" ht="19" customHeight="1">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 545억   ·   현금 9억(1.6%)      당일 2026-07-16  vs  전영업일 2026-07-15      매수 0종목  /  매도 0종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      당일 2026-07-16  vs  전영업일 2026-07-15      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B38" s="4" t="n"/>

--- a/reports/pdf_change_20260716.xlsx
+++ b/reports/pdf_change_20260716.xlsx
@@ -574,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      당일 2026-07-16  vs  전영업일 2026-07-15      매수 12종목  /  매도 11종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,921억   ·   현금 61억(1.3%)      당일 2026-07-16  vs  전영업일 2026-07-15      매수 12종목  /  매도 11종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -669,10 +669,8 @@
       <c r="B6" s="11" t="n">
         <v>211</v>
       </c>
-      <c r="C6" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C6" s="11" t="n">
+        <v>9135456000</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -692,10 +690,8 @@
       <c r="H6" s="15" t="n">
         <v>-34</v>
       </c>
-      <c r="I6" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I6" s="15" t="n">
+        <v>-451321440</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -717,10 +713,8 @@
       <c r="B7" s="11" t="n">
         <v>106</v>
       </c>
-      <c r="C7" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C7" s="11" t="n">
+        <v>1636529760</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -740,10 +734,8 @@
       <c r="H7" s="15" t="n">
         <v>-24</v>
       </c>
-      <c r="I7" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I7" s="15" t="n">
+        <v>-990691200</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -765,10 +757,8 @@
       <c r="B8" s="11" t="n">
         <v>59</v>
       </c>
-      <c r="C8" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C8" s="11" t="n">
+        <v>1109450160</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -788,10 +778,8 @@
       <c r="H8" s="15" t="n">
         <v>-16</v>
       </c>
-      <c r="I8" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I8" s="15" t="n">
+        <v>-415641600</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -813,10 +801,8 @@
       <c r="B9" s="11" t="n">
         <v>51</v>
       </c>
-      <c r="C9" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C9" s="11" t="n">
+        <v>508865760</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
@@ -836,10 +822,8 @@
       <c r="H9" s="15" t="n">
         <v>-16</v>
       </c>
-      <c r="I9" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I9" s="15" t="n">
+        <v>-483340800</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
@@ -861,10 +845,8 @@
       <c r="B10" s="11" t="n">
         <v>37</v>
       </c>
-      <c r="C10" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C10" s="11" t="n">
+        <v>480585600</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
@@ -884,10 +866,8 @@
       <c r="H10" s="15" t="n">
         <v>-15</v>
       </c>
-      <c r="I10" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I10" s="15" t="n">
+        <v>-419184000</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
@@ -909,10 +889,8 @@
       <c r="B11" s="11" t="n">
         <v>33</v>
       </c>
-      <c r="C11" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C11" s="11" t="n">
+        <v>2594512800</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
@@ -932,10 +910,8 @@
       <c r="H11" s="15" t="n">
         <v>-14</v>
       </c>
-      <c r="I11" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I11" s="15" t="n">
+        <v>-932635200</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
@@ -957,10 +933,8 @@
       <c r="B12" s="11" t="n">
         <v>23</v>
       </c>
-      <c r="C12" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C12" s="11" t="n">
+        <v>716302800</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
@@ -980,10 +954,8 @@
       <c r="H12" s="15" t="n">
         <v>-10</v>
       </c>
-      <c r="I12" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I12" s="15" t="n">
+        <v>-2105760000</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
@@ -1005,10 +977,8 @@
       <c r="B13" s="11" t="n">
         <v>18</v>
       </c>
-      <c r="C13" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C13" s="11" t="n">
+        <v>972388800</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
@@ -1028,10 +998,8 @@
       <c r="H13" s="15" t="n">
         <v>-10</v>
       </c>
-      <c r="I13" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I13" s="15" t="n">
+        <v>-470352000</v>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
@@ -1053,10 +1021,8 @@
       <c r="B14" s="11" t="n">
         <v>17</v>
       </c>
-      <c r="C14" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C14" s="11" t="n">
+        <v>945132000</v>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
@@ -1076,10 +1042,8 @@
       <c r="H14" s="15" t="n">
         <v>-10</v>
       </c>
-      <c r="I14" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I14" s="15" t="n">
+        <v>-427056000</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
@@ -1101,10 +1065,8 @@
       <c r="B15" s="11" t="n">
         <v>16</v>
       </c>
-      <c r="C15" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C15" s="11" t="n">
+        <v>2459212800</v>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
@@ -1124,10 +1086,8 @@
       <c r="H15" s="15" t="n">
         <v>-7</v>
       </c>
-      <c r="I15" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I15" s="15" t="n">
+        <v>-982917600</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
@@ -1149,10 +1109,8 @@
       <c r="B16" s="11" t="n">
         <v>11</v>
       </c>
-      <c r="C16" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C16" s="11" t="n">
+        <v>457314000</v>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
@@ -1172,10 +1130,8 @@
       <c r="H16" s="15" t="n">
         <v>-6</v>
       </c>
-      <c r="I16" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I16" s="15" t="n">
+        <v>-228780000</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
@@ -1197,10 +1153,8 @@
       <c r="B17" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="C17" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C17" s="11" t="n">
+        <v>493279200</v>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
@@ -1221,7 +1175,7 @@
     <row r="19" ht="19" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      당일 2026-07-16  vs  전영업일 2026-07-15      매수 0종목  /  매도 0종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 4,238억   ·   현금 11억(0.3%)      당일 2026-07-16  vs  전영업일 2026-07-15      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B19" s="4" t="n"/>
@@ -1245,7 +1199,7 @@
     <row r="22" ht="19" customHeight="1">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      당일 2026-07-16  vs  전영업일 2026-07-15      매수 1종목  /  매도 0종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,884억   ·   현금 28억(1.0%)      당일 2026-07-16  vs  전영업일 2026-07-15      매수 1종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B22" s="4" t="n"/>
@@ -1340,10 +1294,8 @@
       <c r="B25" s="11" t="n">
         <v>122</v>
       </c>
-      <c r="C25" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C25" s="11" t="n">
+        <v>3660976000</v>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
@@ -1364,7 +1316,7 @@
     <row r="27" ht="19" customHeight="1">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      당일 2026-07-16  vs  전영업일 2026-07-15      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,500억   ·   현금 27억(1.1%)      당일 2026-07-16  vs  전영업일 2026-07-15      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B27" s="4" t="n"/>
@@ -1388,7 +1340,7 @@
     <row r="30" ht="19" customHeight="1">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      당일 2026-07-16  vs  전영업일 2026-07-15      매수 2종목  /  매도 4종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 359억   ·   현금 2억(100.0%)      당일 2026-07-16  vs  전영업일 2026-07-15      매수 2종목  /  매도 4종목</t>
         </is>
       </c>
       <c r="B30" s="4" t="n"/>
@@ -1483,14 +1435,12 @@
       <c r="B33" s="11" t="n">
         <v>110</v>
       </c>
-      <c r="C33" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C33" s="11" t="n">
+        <v>78633500</v>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>6.46%→6.68%</t>
         </is>
       </c>
       <c r="E33" s="13" t="inlineStr">
@@ -1506,14 +1456,12 @@
       <c r="H33" s="15" t="n">
         <v>-8</v>
       </c>
-      <c r="I33" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I33" s="15" t="n">
+        <v>-97036000</v>
       </c>
       <c r="J33" s="16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3.16%→2.89%</t>
         </is>
       </c>
       <c r="K33" s="13" t="inlineStr">
@@ -1531,14 +1479,12 @@
       <c r="B34" s="11" t="n">
         <v>55</v>
       </c>
-      <c r="C34" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C34" s="11" t="n">
+        <v>151236250</v>
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>5.52%→5.95%</t>
         </is>
       </c>
       <c r="E34" s="13" t="inlineStr">
@@ -1554,14 +1500,12 @@
       <c r="H34" s="15" t="n">
         <v>-7</v>
       </c>
-      <c r="I34" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I34" s="15" t="n">
+        <v>-92939000</v>
       </c>
       <c r="J34" s="16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3.49%→3.24%</t>
         </is>
       </c>
       <c r="K34" s="13" t="inlineStr">
@@ -1584,14 +1528,12 @@
       <c r="H35" s="15" t="n">
         <v>-4</v>
       </c>
-      <c r="I35" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I35" s="15" t="n">
+        <v>-39406000</v>
       </c>
       <c r="J35" s="16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4.00%→3.89%</t>
         </is>
       </c>
       <c r="K35" s="13" t="inlineStr">
@@ -1614,14 +1556,12 @@
       <c r="H36" s="15" t="n">
         <v>-3</v>
       </c>
-      <c r="I36" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I36" s="15" t="n">
+        <v>-54570000</v>
       </c>
       <c r="J36" s="16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3.57%→3.41%</t>
         </is>
       </c>
       <c r="K36" s="13" t="inlineStr">
@@ -1633,7 +1573,7 @@
     <row r="38" ht="19" customHeight="1">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      당일 2026-07-16  vs  전영업일 2026-07-15      매수 0종목  /  매도 0종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 545억   ·   현금 9억(1.6%)      당일 2026-07-16  vs  전영업일 2026-07-15      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B38" s="4" t="n"/>

--- a/reports/pdf_change_20260716.xlsx
+++ b/reports/pdf_change_20260716.xlsx
@@ -772,23 +772,23 @@
       </c>
       <c r="G8" s="14" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>한중엔시에스</t>
         </is>
       </c>
       <c r="H8" s="15" t="n">
         <v>-16</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-415641600</v>
+        <v>-483340800</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
-          <t>0.40%→0.27%</t>
+          <t>1.01%→0.88%</t>
         </is>
       </c>
       <c r="K8" s="13" t="inlineStr">
         <is>
-          <t>67→51</t>
+          <t>157→141</t>
         </is>
       </c>
     </row>
@@ -816,23 +816,23 @@
       </c>
       <c r="G9" s="14" t="inlineStr">
         <is>
-          <t>한중엔시에스</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="H9" s="15" t="n">
         <v>-16</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-483340800</v>
+        <v>-415641600</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
-          <t>1.01%→0.88%</t>
+          <t>0.40%→0.27%</t>
         </is>
       </c>
       <c r="K9" s="13" t="inlineStr">
         <is>
-          <t>157→141</t>
+          <t>67→51</t>
         </is>
       </c>
     </row>
@@ -992,23 +992,23 @@
       </c>
       <c r="G13" s="14" t="inlineStr">
         <is>
-          <t>에스앤에스텍</t>
+          <t>에이치브이엠</t>
         </is>
       </c>
       <c r="H13" s="15" t="n">
         <v>-10</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-470352000</v>
+        <v>-427056000</v>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
-          <t>0.45%→0.34%</t>
+          <t>0.32%→0.21%</t>
         </is>
       </c>
       <c r="K13" s="13" t="inlineStr">
         <is>
-          <t>45→35</t>
+          <t>34→24</t>
         </is>
       </c>
     </row>
@@ -1036,23 +1036,23 @@
       </c>
       <c r="G14" s="14" t="inlineStr">
         <is>
-          <t>에이치브이엠</t>
+          <t>에스앤에스텍</t>
         </is>
       </c>
       <c r="H14" s="15" t="n">
         <v>-10</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-427056000</v>
+        <v>-470352000</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
-          <t>0.32%→0.21%</t>
+          <t>0.45%→0.34%</t>
         </is>
       </c>
       <c r="K14" s="13" t="inlineStr">
         <is>
-          <t>34→24</t>
+          <t>45→35</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_change_20260716.xlsx
+++ b/reports/pdf_change_20260716.xlsx
@@ -948,23 +948,23 @@
       </c>
       <c r="G12" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>에이치브이엠</t>
         </is>
       </c>
       <c r="H12" s="15" t="n">
         <v>-10</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>-2105760000</v>
+        <v>-427056000</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
-          <t>11.65%→10.22%</t>
+          <t>0.32%→0.21%</t>
         </is>
       </c>
       <c r="K12" s="13" t="inlineStr">
         <is>
-          <t>244→234</t>
+          <t>34→24</t>
         </is>
       </c>
     </row>
@@ -992,23 +992,23 @@
       </c>
       <c r="G13" s="14" t="inlineStr">
         <is>
-          <t>에이치브이엠</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H13" s="15" t="n">
         <v>-10</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-427056000</v>
+        <v>-2105760000</v>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
-          <t>0.32%→0.21%</t>
+          <t>11.65%→10.22%</t>
         </is>
       </c>
       <c r="K13" s="13" t="inlineStr">
         <is>
-          <t>34→24</t>
+          <t>244→234</t>
         </is>
       </c>
     </row>
